--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_audit_log.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D4V151_20260813_083347</t>
+          <t>D4V16_20260917_235626</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>d4-v1.5.1-statistical-dependence-audit-20260813</t>
+          <t>d4-v1.6-neutral-reference-20260917</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-13T08:36:22.471481+00:00</t>
+          <t>2026-09-18T00:05:37.897142+00:00</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9888907041333116</v>
+        <v>0.9846430321842836</v>
       </c>
     </row>
     <row r="21">
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,139 +768,117 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-10T09:12:59.533264+00:00</t>
+          <t>2026-08-19T07:19:59.641240+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>d1_scores</t>
+          <t>raw_observations</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D1_main_scores_min.xlsx</t>
+          <t>time_base_1min_raw.parquet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>83207ca6f818dd309fe36cdb3adfdc9e569ea540fbca5c4acc0e45e8a321923c</t>
+          <t>df2acf4d548b8e6faee0bda3c73ea195fe131ca56a4fa8e8f3a72614c71dd7e5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27T08:02:48.122703+00:00</t>
+          <t>2026-07-10T09:12:59.001761+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>regime_templates</t>
+          <t>d4_config</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D1_regime_templates.xlsx</t>
+          <t>d4.yaml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3dcbb33f64e2b3ece25d6dddd57421cf2d2651e6324f5cd26e1b191fa6aab169</t>
+          <t>627c2df190e99dabe7f637b01286a3f978c118f8fefe1944468756d23db910ef</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27T08:02:48.137757+00:00</t>
+          <t>2026-09-17T12:42:03.921422+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>d2_scores</t>
+          <t>d4_pipeline_code</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D2_main_scores_hourly.xlsx</t>
+          <t>pipeline.py</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ac051d9a24a17523433c63187cf63f0128efb185325a1ea789633f7fc13d04a6</t>
+          <t>68b82941af9871d24c60d3d9f108d20d9df2d4fc3956e0aaf39ad8d37eb08e30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-05T03:28:59.791070+00:00</t>
+          <t>2026-09-17T23:55:19.557220+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>d4_config</t>
+          <t>d4_scoring_code</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d4.yaml</t>
+          <t>scoring.py</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>213ecde94309486e5a09659e2306c3028459cc77786e175b98e381cba198df74</t>
+          <t>e165baa56d22c1dc5302eb0efc2c2dd85209ad3fdfd60c249ba76a64ed4b81cb</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-13T08:26:25.369829+00:00</t>
+          <t>2026-08-19T07:20:01.900694+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>d4_pipeline_code</t>
+          <t>shared_context_code</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pipeline.py</t>
+          <t>context.py</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4c9dfbaa3c0068d0476fd8a2f6a1602802bacb31bb9c6c60f5bf7dfa0f79c5a6</t>
+          <t>9292cf3e0aafad7b7fc811bc2d8d2d4a08226e1e1efec8fabed480708fecb813</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-13T08:33:10.776586+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>d4_scoring_code</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>scoring.py</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1f7845876b73515ea34171dd34a50d279aa32d0fd3244226b8ab9774292f4bfe</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-08-13T02:48:32.786982+00:00</t>
+          <t>2026-09-17T12:39:46.686292+00:00</t>
         </is>
       </c>
     </row>
@@ -938,7 +916,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D2 continuity</t>
+          <t>shared raw support</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -955,17 +933,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D1 bilateral fuse</t>
+          <t>D1 interpretation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>true v1.2 fuse</t>
+          <t>post-score join only</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>D4_after_D1</t>
+          <t>D1_target;D1_ref</t>
         </is>
       </c>
     </row>
